--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:36:19+00:00</t>
+    <t>2024-04-03T13:59:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>
@@ -597,7 +597,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-source-information-installation</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/VS-TRE-R301-SourceInformationInstallation</t>
   </si>
   <si>
     <t>base64Binary
@@ -939,7 +939,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="85.83984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="92.07421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:18:25+00:00</t>
+    <t>2024-04-03T14:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:35:17+00:00</t>
+    <t>2024-04-03T14:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:14:28+00:00</t>
+    <t>2024-04-08T13:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:35:38+00:00</t>
+    <t>2024-04-08T14:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,9 +319,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:dateAuthorization</t>
   </si>
   <si>
@@ -368,6 +365,9 @@
     <t>Extension.url</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:dateAuthorization.value[x]</t>
   </si>
   <si>
@@ -450,8 +450,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>./low</t>
@@ -1367,24 +1367,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1409,10 +1409,10 @@
         <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1472,7 +1472,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1586,10 +1586,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1618,7 +1618,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1678,7 +1678,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1715,16 +1715,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1774,22 +1774,22 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1886,13 +1886,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -1931,7 +1931,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1991,7 +1991,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -2005,7 +2005,7 @@
         <v>124</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2108,7 +2108,7 @@
         <v>125</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2137,7 +2137,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2197,7 +2197,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2211,7 +2211,7 @@
         <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2234,16 +2234,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2293,22 +2293,22 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2405,13 +2405,13 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -2613,13 +2613,13 @@
         <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
@@ -2870,7 +2870,7 @@
         <v>153</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2930,7 +2930,7 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>81</v>
@@ -2944,7 +2944,7 @@
         <v>154</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3047,7 +3047,7 @@
         <v>155</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3076,7 +3076,7 @@
         <v>30</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3136,7 +3136,7 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>81</v>
@@ -3150,7 +3150,7 @@
         <v>156</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3173,16 +3173,16 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3232,22 +3232,22 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="23">
@@ -3344,13 +3344,13 @@
         <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24">
@@ -3389,7 +3389,7 @@
         <v>160</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3449,7 +3449,7 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>81</v>
@@ -3463,7 +3463,7 @@
         <v>161</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3566,7 +3566,7 @@
         <v>162</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3595,7 +3595,7 @@
         <v>30</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3655,7 +3655,7 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>81</v>
@@ -3669,7 +3669,7 @@
         <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3692,16 +3692,16 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3751,22 +3751,22 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="28">
@@ -3863,13 +3863,13 @@
         <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29">
@@ -3908,7 +3908,7 @@
         <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3968,7 +3968,7 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>81</v>
@@ -3982,7 +3982,7 @@
         <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4085,7 +4085,7 @@
         <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4114,7 +4114,7 @@
         <v>30</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4174,7 +4174,7 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>81</v>
@@ -4188,7 +4188,7 @@
         <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4211,16 +4211,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4270,22 +4270,22 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="33">
@@ -4382,13 +4382,13 @@
         <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34">
@@ -4427,7 +4427,7 @@
         <v>175</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4487,7 +4487,7 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>81</v>
@@ -4501,7 +4501,7 @@
         <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4604,7 +4604,7 @@
         <v>177</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4633,7 +4633,7 @@
         <v>30</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4693,7 +4693,7 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>81</v>
@@ -4707,7 +4707,7 @@
         <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4730,16 +4730,16 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4789,22 +4789,22 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="38">
@@ -4901,13 +4901,13 @@
         <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39">
@@ -4946,7 +4946,7 @@
         <v>182</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5006,7 +5006,7 @@
         <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>81</v>
@@ -5020,7 +5020,7 @@
         <v>183</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5123,7 +5123,7 @@
         <v>184</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5152,7 +5152,7 @@
         <v>30</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5212,7 +5212,7 @@
         <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>81</v>
@@ -5226,7 +5226,7 @@
         <v>185</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5249,16 +5249,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5308,22 +5308,22 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK42" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="43">
@@ -5418,21 +5418,21 @@
         <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5455,16 +5455,16 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5514,22 +5514,22 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="45">
@@ -5626,13 +5626,13 @@
         <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T14:07:36+00:00</t>
+    <t>2024-04-08T14:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
